--- a/swing_trade_bot/output/latest.xlsx
+++ b/swing_trade_bot/output/latest.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Market Overview" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top 10 Swing Trades" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Buy Signals" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Technical Charts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trading Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,11 +20,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -75,7 +80,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00BF8F00"/>
+      <color rgb="00006100"/>
       <sz val="10"/>
     </font>
     <font>
@@ -87,11 +92,40 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00006100"/>
-      <sz val="10"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00BF8F00"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="14"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -120,11 +154,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
@@ -136,6 +165,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,7 +196,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -189,17 +228,83 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -208,36 +313,42 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -312,6 +423,261 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>43</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>82</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>160</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>199</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>238</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>277</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>316</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>355</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="9334500" cy="6667500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,7 +991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: February 19, 2026 at 06:23 PM CST</t>
+          <t>Generated: March 04, 2026 at 04:49 PM CST</t>
         </is>
       </c>
     </row>
@@ -672,16 +1038,16 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>6883</v>
+        <v>6879</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>+6.0</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
@@ -697,16 +1063,16 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>24891.75</v>
+        <v>25138</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>+33.0</t>
+          <t>+9.75</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -722,21 +1088,21 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>49474</v>
+        <v>48811</v>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>+16.0</t>
+          <t>+251.0</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.52%</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>SLIGHTLY BULLISH</t>
+          <t>BULLISH</t>
         </is>
       </c>
     </row>
@@ -747,16 +1113,16 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>2668.5</v>
+        <v>2636.7</v>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="E9" s="10" t="inlineStr">
@@ -772,21 +1138,21 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>20.23</v>
-      </c>
-      <c r="C10" s="7" t="inlineStr">
-        <is>
-          <t>+0.61</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>+3.11%</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>INCREASING FEAR</t>
+        <v>21.15</v>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>-2.42</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>-10.27%</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>DECREASING FEAR</t>
         </is>
       </c>
     </row>
@@ -801,17 +1167,17 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>+-0.0</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>-0.1%</t>
-        </is>
-      </c>
-      <c r="E11" s="10" t="inlineStr">
-        <is>
-          <t>NEUTRAL</t>
+          <t>+0.02</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>+0.59%</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>BULLISH</t>
         </is>
       </c>
     </row>
@@ -822,16 +1188,16 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>97.81999999999999</v>
+        <v>98.81</v>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.24</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>-0.11%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -841,39 +1207,39 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>⚡ FUTURES VERDICT: MIXED (3/7 indicators positive). Plan swing entries accordingly.</t>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>FUTURES VERDICT: BULLISH (5/7 indicators positive)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="13" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>OVERALL MARKET &amp; FEDERAL RESERVE STATUS</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="14" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="B16" s="14" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C16" s="14" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D16" s="14" t="inlineStr"/>
-      <c r="E16" s="14" t="inlineStr"/>
-      <c r="F16" s="14" t="inlineStr"/>
-      <c r="G16" s="14" t="inlineStr"/>
+      <c r="D16" s="13" t="inlineStr"/>
+      <c r="E16" s="13" t="inlineStr"/>
+      <c r="F16" s="13" t="inlineStr"/>
+      <c r="G16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -917,7 +1283,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Rates held steady at Jan 27-28 meeting. 2 dissents favored a cut.</t>
+          <t>Rates held at Jan 27-28 meeting. 2 dissents favored cut.</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -951,7 +1317,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>93% probability rates held in March; ~65bps of cuts priced for 2026</t>
+          <t>93% prob rates held in March; ~65bps cuts priced for 2026</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1009,7 +1375,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Updated: February 19, 2026 at 06:23 PM CST | Top 3 highlighted in yellow</t>
+          <t>Updated: March 04, 2026 at 04:49 PM CST | Top 3 highlighted in yellow</t>
         </is>
       </c>
     </row>
@@ -1096,582 +1462,582 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="16" t="inlineStr">
+      <c r="B4" s="15" t="inlineStr">
         <is>
           <t>MU</t>
         </is>
       </c>
-      <c r="C4" s="17" t="inlineStr">
+      <c r="C4" s="16" t="inlineStr">
         <is>
           <t>Micron Technology, Inc.</t>
         </is>
       </c>
-      <c r="D4" s="15" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>Semiconductors</t>
         </is>
       </c>
-      <c r="E4" s="18" t="n">
-        <v>417.35</v>
-      </c>
-      <c r="F4" s="18" t="n">
-        <v>420.95</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <v>207.29</v>
-      </c>
-      <c r="H4" s="19" t="n">
-        <v>-0.0086</v>
-      </c>
-      <c r="I4" s="20" t="n">
-        <v>1.0134</v>
-      </c>
-      <c r="J4" s="21" t="n">
-        <v>469.7</v>
-      </c>
-      <c r="K4" s="21" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="L4" s="16" t="n">
-        <v>84</v>
-      </c>
-      <c r="M4" s="15" t="n">
+      <c r="E4" s="17" t="n">
+        <v>400.77</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="G4" s="17" t="n">
+        <v>226.56</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <v>0.0555</v>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>0.7689</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>451.1</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="M4" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="N4" s="15" t="n">
+      <c r="N4" s="14" t="n">
         <v>35</v>
       </c>
-      <c r="O4" s="15" t="n">
+      <c r="O4" s="14" t="n">
+        <v>15</v>
+      </c>
+      <c r="P4" s="14" t="inlineStr">
+        <is>
+          <t>$61.54 - $455.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Strategy Inc</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>Crypto / Software</t>
+        </is>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>146.44</v>
+      </c>
+      <c r="F5" s="17" t="n">
+        <v>132.68</v>
+      </c>
+      <c r="G5" s="17" t="n">
+        <v>186.01</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.1037</v>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>-0.2127</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="L5" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>11</v>
+      </c>
+      <c r="P5" s="14" t="inlineStr">
+        <is>
+          <t>$104.17 - $457.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="15" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>EV / Automotive</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>405.94</v>
+      </c>
+      <c r="F6" s="17" t="n">
+        <v>392.43</v>
+      </c>
+      <c r="G6" s="17" t="n">
+        <v>454.53</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.0344</v>
+      </c>
+      <c r="I6" s="20" t="n">
+        <v>-0.1069</v>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>1523.3</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="L6" s="15" t="n">
+        <v>68</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>35</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>24</v>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>$214.25 - $498.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>183.04</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>180.05</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>183.38</v>
+      </c>
+      <c r="H7" s="24" t="n">
+        <v>0.0166</v>
+      </c>
+      <c r="I7" s="25" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="J7" s="26" t="n">
+        <v>4448.8</v>
+      </c>
+      <c r="K7" s="26" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="L7" s="10" t="n">
+        <v>67</v>
+      </c>
+      <c r="M7" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="N7" s="21" t="n">
+        <v>2</v>
+      </c>
+      <c r="O7" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t>$86.62 - $212.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>AI / Software</t>
+        </is>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>153.19</v>
+      </c>
+      <c r="F8" s="23" t="n">
+        <v>147.22</v>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>177.92</v>
+      </c>
+      <c r="H8" s="24" t="n">
+        <v>0.0406</v>
+      </c>
+      <c r="I8" s="25" t="n">
+        <v>-0.139</v>
+      </c>
+      <c r="J8" s="26" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="L8" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="M8" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="N8" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O8" s="21" t="n">
+        <v>19</v>
+      </c>
+      <c r="P8" s="21" t="inlineStr">
+        <is>
+          <t>$66.12 - $207.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="D9" s="21" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>202.07</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>190.95</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>215.98</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>0.0582</v>
+      </c>
+      <c r="I9" s="25" t="n">
+        <v>-0.0644</v>
+      </c>
+      <c r="J9" s="26" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="L9" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="M9" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="N9" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="P9" s="21" t="inlineStr">
+        <is>
+          <t>$76.48 - $267.08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>317.53</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>313.84</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>380.3</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="I10" s="25" t="n">
+        <v>-0.1651</v>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>1505.5</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>57</v>
+      </c>
+      <c r="M10" s="21" t="n">
+        <v>35</v>
+      </c>
+      <c r="N10" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="O10" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="P4" s="15" t="inlineStr">
-        <is>
-          <t>$61.54 – $455.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
-        <is>
-          <t>NVDA</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>NVIDIA Corporation</t>
-        </is>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>187.9</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>187.98</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>178.87</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0004</v>
-      </c>
-      <c r="I5" s="20" t="n">
-        <v>0.0505</v>
-      </c>
-      <c r="J5" s="21" t="n">
-        <v>4574.8</v>
-      </c>
-      <c r="K5" s="21" t="n">
-        <v>180</v>
-      </c>
-      <c r="L5" s="16" t="n">
-        <v>67</v>
-      </c>
-      <c r="M5" s="15" t="n">
+      <c r="P10" s="21" t="inlineStr">
+        <is>
+          <t>$138.10 - $414.61</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>CrowdStrike Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>407.68</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>391.42</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>513.12</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>0.0415</v>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>-0.2055</v>
+      </c>
+      <c r="J11" s="26" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="K11" s="26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>52</v>
+      </c>
+      <c r="M11" s="21" t="n">
+        <v>32</v>
+      </c>
+      <c r="N11" s="21" t="n">
+        <v>14</v>
+      </c>
+      <c r="O11" s="21" t="n">
+        <v>6</v>
+      </c>
+      <c r="P11" s="21" t="inlineStr">
+        <is>
+          <t>$298.00 - $566.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="inlineStr">
+        <is>
+          <t>Streaming / Media</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>97.7</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>103.22</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.0098</v>
+      </c>
+      <c r="I12" s="25" t="n">
+        <v>-0.0442</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M12" s="21" t="n">
+        <v>27</v>
+      </c>
+      <c r="N12" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="P12" s="21" t="inlineStr">
+        <is>
+          <t>$75.01 - $134.12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>158.56</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>156.09</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>195.68</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>0.0158</v>
+      </c>
+      <c r="I13" s="25" t="n">
+        <v>-0.1897</v>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L13" s="10" t="n">
         <v>35</v>
       </c>
-      <c r="N5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="O5" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="P5" s="15" t="inlineStr">
-        <is>
-          <t>$86.62 – $212.19</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Strategy Inc</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>Crypto / Software</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>129.45</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>125.2</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>170.5</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <v>0.0339</v>
-      </c>
-      <c r="I6" s="19" t="n">
-        <v>-0.2408</v>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>43</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>23.2</v>
-      </c>
-      <c r="L6" s="16" t="n">
-        <v>60</v>
-      </c>
-      <c r="M6" s="15" t="n">
-        <v>35</v>
-      </c>
-      <c r="N6" s="15" t="n">
-        <v>14</v>
-      </c>
-      <c r="O6" s="15" t="n">
-        <v>11</v>
-      </c>
-      <c r="P6" s="15" t="inlineStr">
-        <is>
-          <t>$104.17 – $457.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>TSLA</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Tesla, Inc.</t>
-        </is>
-      </c>
-      <c r="D7" s="22" t="inlineStr">
-        <is>
-          <t>EV / Automotive</t>
-        </is>
-      </c>
-      <c r="E7" s="24" t="n">
-        <v>411.71</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <v>411.22</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>391.09</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <v>0.0012</v>
-      </c>
-      <c r="I7" s="25" t="n">
-        <v>0.0527</v>
-      </c>
-      <c r="J7" s="26" t="n">
-        <v>1544.9</v>
-      </c>
-      <c r="K7" s="26" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="L7" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="M7" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="N7" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O7" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="P7" s="22" t="inlineStr">
-        <is>
-          <t>$214.25 – $498.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>PLTR</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Palantir Technologies Inc.</t>
-        </is>
-      </c>
-      <c r="D8" s="22" t="inlineStr">
-        <is>
-          <t>AI / Software</t>
-        </is>
-      </c>
-      <c r="E8" s="24" t="n">
-        <v>134.89</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>135.38</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>154.85</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.0036</v>
-      </c>
-      <c r="I8" s="27" t="n">
-        <v>-0.1289</v>
-      </c>
-      <c r="J8" s="26" t="n">
-        <v>321.5</v>
-      </c>
-      <c r="K8" s="26" t="n">
-        <v>44.8</v>
-      </c>
-      <c r="L8" s="11" t="n">
-        <v>58</v>
-      </c>
-      <c r="M8" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="N8" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="O8" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="P8" s="22" t="inlineStr">
-        <is>
-          <t>$66.12 – $207.52</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>NFLX</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Netflix, Inc.</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>Streaming / Media</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>77</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>77.98999999999999</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>104.31</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-0.0127</v>
-      </c>
-      <c r="I9" s="27" t="n">
-        <v>-0.2618</v>
-      </c>
-      <c r="J9" s="26" t="n">
-        <v>326.6</v>
-      </c>
-      <c r="K9" s="26" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="L9" s="11" t="n">
-        <v>57</v>
-      </c>
-      <c r="M9" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="N9" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="O9" s="22" t="n">
+      <c r="M13" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="P9" s="22" t="inlineStr">
-        <is>
-          <t>$75.23 – $134.12</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="N13" s="21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O13" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Advanced Micro Devices, Inc.</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>203.37</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>200.12</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>203.78</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>0.0162</v>
-      </c>
-      <c r="I10" s="27" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="J10" s="26" t="n">
-        <v>331.6</v>
-      </c>
-      <c r="K10" s="26" t="n">
-        <v>37.3</v>
-      </c>
-      <c r="L10" s="11" t="n">
-        <v>53</v>
-      </c>
-      <c r="M10" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="N10" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="O10" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="P10" s="22" t="inlineStr">
-        <is>
-          <t>$76.48 – $267.08</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>AVGO</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Broadcom Inc.</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>Semiconductors</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>333.99</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>333.51</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>339.55</v>
-      </c>
-      <c r="H11" s="25" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="I11" s="27" t="n">
-        <v>-0.0164</v>
-      </c>
-      <c r="J11" s="26" t="n">
-        <v>1583.5</v>
-      </c>
-      <c r="K11" s="26" t="n">
-        <v>31.7</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>49</v>
-      </c>
-      <c r="M11" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="N11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="P11" s="22" t="inlineStr">
-        <is>
-          <t>$138.10 – $414.61</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>CRWD</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>CrowdStrike Holdings, Inc.</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>422.14</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>415.76</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>490.67</v>
-      </c>
-      <c r="H12" s="25" t="n">
-        <v>0.0153</v>
-      </c>
-      <c r="I12" s="27" t="n">
-        <v>-0.1397</v>
-      </c>
-      <c r="J12" s="26" t="n">
-        <v>106.4</v>
-      </c>
-      <c r="K12" s="26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="M12" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="N12" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="O12" s="22" t="n">
-        <v>5</v>
-      </c>
-      <c r="P12" s="22" t="inlineStr">
-        <is>
-          <t>$298.00 – $566.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>PANW</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Palo Alto Networks, Inc.</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>Cybersecurity</t>
-        </is>
-      </c>
-      <c r="E13" s="24" t="n">
-        <v>150.99</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>152.35</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>182.9</v>
-      </c>
-      <c r="H13" s="27" t="n">
-        <v>-0.0089</v>
-      </c>
-      <c r="I13" s="27" t="n">
-        <v>-0.1745</v>
-      </c>
-      <c r="J13" s="26" t="n">
-        <v>122</v>
-      </c>
-      <c r="K13" s="26" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="L13" s="11" t="n">
-        <v>32</v>
-      </c>
-      <c r="M13" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="N13" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="O13" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="P13" s="22" t="inlineStr">
-        <is>
-          <t>$144.15 – $223.61</t>
+      <c r="P13" s="21" t="inlineStr">
+        <is>
+          <t>$139.57 - $223.61</t>
         </is>
       </c>
     </row>
@@ -1682,4 +2048,1567 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="40" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TECHNICAL BUY SIGNAL ANALYSIS — NASDAQ Stocks (Mkt Cap &gt; $1B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Updated: March 04, 2026 at 04:49 PM CST | BUY = Score 70+ | WATCH = 45-69 | AVOID = Below 45</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Company</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Mkt Cap ($B)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Buy Score</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Rating</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>RSI (14)</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>MACD</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MACD Signal</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>MACD Cross</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>BB Position %</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>50-SMA</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>200-SMA</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Above 50-SMA</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Above 200-SMA</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Golden Cross</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Vol Ratio</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>Vol Surge</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>From 52wk High</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>From 52wk Low</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Key Reasons</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>CRWD</t>
+        </is>
+      </c>
+      <c r="B4" s="28" t="inlineStr">
+        <is>
+          <t>CrowdStrike Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D4" s="30" t="n">
+        <v>407.68</v>
+      </c>
+      <c r="E4" s="31" t="n">
+        <v>102.8</v>
+      </c>
+      <c r="F4" s="32" t="n">
+        <v>45</v>
+      </c>
+      <c r="G4" s="33" t="inlineStr">
+        <is>
+          <t>WATCH</t>
+        </is>
+      </c>
+      <c r="H4" s="34" t="n">
+        <v>47.9</v>
+      </c>
+      <c r="I4" s="35" t="n">
+        <v>-15.43</v>
+      </c>
+      <c r="J4" s="35" t="n">
+        <v>-18.49</v>
+      </c>
+      <c r="K4" s="27" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L4" s="34" t="n">
+        <v>62.9</v>
+      </c>
+      <c r="M4" s="30" t="n">
+        <v>435.44</v>
+      </c>
+      <c r="N4" s="30" t="n">
+        <v>407.6799926757812</v>
+      </c>
+      <c r="O4" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P4" s="27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R4" s="35" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="T4" s="36" t="n">
+        <v>-26.9</v>
+      </c>
+      <c r="U4" s="37" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="V4" s="28" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA) | Volume surge 1.54x on up day</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>Tesla, Inc.</t>
+        </is>
+      </c>
+      <c r="C5" s="40" t="inlineStr">
+        <is>
+          <t>EV / Automotive</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="n">
+        <v>405.94</v>
+      </c>
+      <c r="E5" s="42" t="n">
+        <v>1523.3</v>
+      </c>
+      <c r="F5" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="G5" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H5" s="45" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="I5" s="46" t="n">
+        <v>-7.51</v>
+      </c>
+      <c r="J5" s="46" t="n">
+        <v>-7.37</v>
+      </c>
+      <c r="K5" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L5" s="45" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="M5" s="41" t="n">
+        <v>431.36</v>
+      </c>
+      <c r="N5" s="41" t="n">
+        <v>405.9400024414062</v>
+      </c>
+      <c r="O5" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P5" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R5" s="46" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="S5" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T5" s="47" t="n">
+        <v>-17.1</v>
+      </c>
+      <c r="U5" s="48" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="V5" s="39" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>AVGO</t>
+        </is>
+      </c>
+      <c r="B6" s="39" t="inlineStr">
+        <is>
+          <t>Broadcom Inc.</t>
+        </is>
+      </c>
+      <c r="C6" s="40" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="D6" s="41" t="n">
+        <v>317.53</v>
+      </c>
+      <c r="E6" s="42" t="n">
+        <v>1505.5</v>
+      </c>
+      <c r="F6" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="G6" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H6" s="45" t="n">
+        <v>30.3</v>
+      </c>
+      <c r="I6" s="46" t="n">
+        <v>-4.71</v>
+      </c>
+      <c r="J6" s="46" t="n">
+        <v>-3.55</v>
+      </c>
+      <c r="K6" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L6" s="45" t="n">
+        <v>26.1</v>
+      </c>
+      <c r="M6" s="41" t="n">
+        <v>334.68</v>
+      </c>
+      <c r="N6" s="41" t="n">
+        <v>317.5299987792969</v>
+      </c>
+      <c r="O6" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P6" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R6" s="46" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="S6" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T6" s="47" t="n">
+        <v>-23</v>
+      </c>
+      <c r="U6" s="48" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="V6" s="39" t="inlineStr">
+        <is>
+          <t>RSI oversold (30.3) | Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>PANW</t>
+        </is>
+      </c>
+      <c r="B7" s="39" t="inlineStr">
+        <is>
+          <t>Palo Alto Networks, Inc.</t>
+        </is>
+      </c>
+      <c r="C7" s="40" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="n">
+        <v>158.56</v>
+      </c>
+      <c r="E7" s="42" t="n">
+        <v>129.4</v>
+      </c>
+      <c r="F7" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="G7" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H7" s="45" t="n">
+        <v>43.2</v>
+      </c>
+      <c r="I7" s="46" t="n">
+        <v>-6.48</v>
+      </c>
+      <c r="J7" s="46" t="n">
+        <v>-7.86</v>
+      </c>
+      <c r="K7" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L7" s="45" t="n">
+        <v>58.2</v>
+      </c>
+      <c r="M7" s="41" t="n">
+        <v>173.12</v>
+      </c>
+      <c r="N7" s="41" t="n">
+        <v>158.5599975585938</v>
+      </c>
+      <c r="O7" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P7" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R7" s="46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="S7" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T7" s="47" t="n">
+        <v>-28.4</v>
+      </c>
+      <c r="U7" s="48" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="V7" s="39" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+      <c r="B8" s="39" t="inlineStr">
+        <is>
+          <t>Micron Technology, Inc.</t>
+        </is>
+      </c>
+      <c r="C8" s="40" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="D8" s="41" t="n">
+        <v>400.77</v>
+      </c>
+      <c r="E8" s="42" t="n">
+        <v>451.1</v>
+      </c>
+      <c r="F8" s="43" t="n">
+        <v>35</v>
+      </c>
+      <c r="G8" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H8" s="45" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I8" s="46" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="J8" s="46" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="K8" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L8" s="45" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="M8" s="41" t="n">
+        <v>371.21</v>
+      </c>
+      <c r="N8" s="41" t="n">
+        <v>400.7699890136719</v>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P8" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q8" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R8" s="46" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S8" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T8" s="47" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="U8" s="48" t="n">
+        <v>205.4</v>
+      </c>
+      <c r="V8" s="39" t="inlineStr">
+        <is>
+          <t>No strong signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>NVDA</t>
+        </is>
+      </c>
+      <c r="B9" s="39" t="inlineStr">
+        <is>
+          <t>NVIDIA Corporation</t>
+        </is>
+      </c>
+      <c r="C9" s="40" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="D9" s="41" t="n">
+        <v>183.04</v>
+      </c>
+      <c r="E9" s="42" t="n">
+        <v>4448.8</v>
+      </c>
+      <c r="F9" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="G9" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H9" s="45" t="n">
+        <v>42.9</v>
+      </c>
+      <c r="I9" s="46" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="J9" s="46" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K9" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L9" s="45" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="M9" s="41" t="n">
+        <v>186.08</v>
+      </c>
+      <c r="N9" s="41" t="n">
+        <v>183.0399932861328</v>
+      </c>
+      <c r="O9" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P9" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R9" s="46" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="S9" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T9" s="47" t="n">
+        <v>-11.6</v>
+      </c>
+      <c r="U9" s="48" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="V9" s="39" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="38" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="B10" s="39" t="inlineStr">
+        <is>
+          <t>Strategy Inc</t>
+        </is>
+      </c>
+      <c r="C10" s="40" t="inlineStr">
+        <is>
+          <t>Crypto / Software</t>
+        </is>
+      </c>
+      <c r="D10" s="41" t="n">
+        <v>146.44</v>
+      </c>
+      <c r="E10" s="42" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="F10" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="G10" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H10" s="45" t="n">
+        <v>62.6</v>
+      </c>
+      <c r="I10" s="46" t="n">
+        <v>-3.54</v>
+      </c>
+      <c r="J10" s="46" t="n">
+        <v>-6.46</v>
+      </c>
+      <c r="K10" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L10" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M10" s="41" t="n">
+        <v>147.81</v>
+      </c>
+      <c r="N10" s="41" t="n">
+        <v>146.4400024414062</v>
+      </c>
+      <c r="O10" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P10" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R10" s="46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T10" s="47" t="n">
+        <v>-59.3</v>
+      </c>
+      <c r="U10" s="48" t="n">
+        <v>36.9</v>
+      </c>
+      <c r="V10" s="39" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="B11" s="39" t="inlineStr">
+        <is>
+          <t>Advanced Micro Devices, Inc.</t>
+        </is>
+      </c>
+      <c r="C11" s="40" t="inlineStr">
+        <is>
+          <t>Semiconductors</t>
+        </is>
+      </c>
+      <c r="D11" s="41" t="n">
+        <v>202.07</v>
+      </c>
+      <c r="E11" s="42" t="n">
+        <v>329.5</v>
+      </c>
+      <c r="F11" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H11" s="45" t="n">
+        <v>42.6</v>
+      </c>
+      <c r="I11" s="46" t="n">
+        <v>-6.62</v>
+      </c>
+      <c r="J11" s="46" t="n">
+        <v>-6.19</v>
+      </c>
+      <c r="K11" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L11" s="45" t="n">
+        <v>43</v>
+      </c>
+      <c r="M11" s="41" t="n">
+        <v>218.34</v>
+      </c>
+      <c r="N11" s="41" t="n">
+        <v>202.0700073242188</v>
+      </c>
+      <c r="O11" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P11" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R11" s="46" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="S11" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T11" s="47" t="n">
+        <v>-23.6</v>
+      </c>
+      <c r="U11" s="48" t="n">
+        <v>33.7</v>
+      </c>
+      <c r="V11" s="39" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B12" s="39" t="inlineStr">
+        <is>
+          <t>Netflix, Inc.</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>Streaming / Media</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="E12" s="42" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="F12" s="43" t="n">
+        <v>25</v>
+      </c>
+      <c r="G12" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H12" s="45" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="I12" s="46" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="J12" s="46" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="K12" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L12" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M12" s="41" t="n">
+        <v>86.55</v>
+      </c>
+      <c r="N12" s="41" t="n">
+        <v>98.66000366210938</v>
+      </c>
+      <c r="O12" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P12" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q12" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R12" s="46" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="S12" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T12" s="47" t="n">
+        <v>-21.9</v>
+      </c>
+      <c r="U12" s="48" t="n">
+        <v>30.1</v>
+      </c>
+      <c r="V12" s="39" t="inlineStr">
+        <is>
+          <t>RSI overbought (78.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="B13" s="39" t="inlineStr">
+        <is>
+          <t>Palantir Technologies Inc.</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>AI / Software</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="n">
+        <v>153.19</v>
+      </c>
+      <c r="E13" s="42" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="F13" s="43" t="n">
+        <v>20</v>
+      </c>
+      <c r="G13" s="44" t="inlineStr">
+        <is>
+          <t>AVOID</t>
+        </is>
+      </c>
+      <c r="H13" s="45" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="I13" s="46" t="n">
+        <v>-3.46</v>
+      </c>
+      <c r="J13" s="46" t="n">
+        <v>-6.91</v>
+      </c>
+      <c r="K13" s="38" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="L13" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="M13" s="41" t="n">
+        <v>158.97</v>
+      </c>
+      <c r="N13" s="41" t="n">
+        <v>153.1900024414062</v>
+      </c>
+      <c r="O13" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P13" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="R13" s="46" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="S13" s="38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T13" s="47" t="n">
+        <v>-26.1</v>
+      </c>
+      <c r="U13" s="48" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="V13" s="39" t="inlineStr">
+        <is>
+          <t>Golden cross (50&gt;200 SMA)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>BUY SCORE METHODOLOGY (0-100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>Max Points</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>What It Measures</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Buy Signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="inlineStr">
+        <is>
+          <t>RSI (14-day)</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>25 pts</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Overbought/oversold momentum</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>Below 30 = oversold = strong buy signal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>MACD Crossover</t>
+        </is>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>20 pts</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Trend change detection</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>MACD crossing above signal line = bullish</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>Bollinger Band Position</t>
+        </is>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>20 pts</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Price vs statistical range</t>
+        </is>
+      </c>
+      <c r="D20" s="21" t="inlineStr">
+        <is>
+          <t>Near lower band (&lt;20%) = potential bounce</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Moving Averages (50/200)</t>
+        </is>
+      </c>
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>20 pts</t>
+        </is>
+      </c>
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Trend direction &amp; support</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>Golden cross + above both SMAs = strong uptrend</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>Volume Surge</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>15 pts</t>
+        </is>
+      </c>
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Institutional buying pressure</t>
+        </is>
+      </c>
+      <c r="D22" s="21" t="inlineStr">
+        <is>
+          <t>Volume &gt;1.5x average on up day = accumulation</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="21" t="inlineStr"/>
+      <c r="B23" s="21" t="inlineStr"/>
+      <c r="C23" s="21" t="inlineStr"/>
+      <c r="D23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="21" t="inlineStr">
+        <is>
+          <t>RATINGS:</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr"/>
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>BUY (70-100) = Strong technicals, consider entry</t>
+        </is>
+      </c>
+      <c r="D24" s="21" t="inlineStr">
+        <is>
+          <t>WATCH (45-69) = Mixed signals, wait for confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr"/>
+      <c r="B25" s="21" t="inlineStr"/>
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>AVOID (0-44) = Weak technicals, stay away for now</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:V2"/>
+    <mergeCell ref="A1:V1"/>
+    <mergeCell ref="A16:V16"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N355"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TECHNICAL ANALYSIS CHARTS — 6-Month Price + Indicators</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Updated: March 04, 2026 at 04:49 PM CST | Each chart: Price + Bollinger + 50/200 SMA + Volume + RSI + MACD</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="49" t="inlineStr">
+        <is>
+          <t>NVDA — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="49" t="inlineStr">
+        <is>
+          <t>MSTR — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="49" t="inlineStr">
+        <is>
+          <t>PLTR — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="49" t="inlineStr">
+        <is>
+          <t>TSLA — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="49" t="inlineStr">
+        <is>
+          <t>AMD — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="49" t="inlineStr">
+        <is>
+          <t>AVGO — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="49" t="inlineStr">
+        <is>
+          <t>PANW — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="50" t="inlineStr">
+        <is>
+          <t>CRWD — Rating: WATCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="49" t="inlineStr">
+        <is>
+          <t>MU — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="49" t="inlineStr">
+        <is>
+          <t>NFLX — Rating: AVOID</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A238:N238"/>
+    <mergeCell ref="A4:N4"/>
+    <mergeCell ref="A355:N355"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A82:N82"/>
+    <mergeCell ref="A199:N199"/>
+    <mergeCell ref="A43:N43"/>
+    <mergeCell ref="A316:N316"/>
+    <mergeCell ref="A121:N121"/>
+    <mergeCell ref="A160:N160"/>
+    <mergeCell ref="A277:N277"/>
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="51" t="inlineStr">
+        <is>
+          <t>TRADING NOTES &amp; RISK FACTORS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="52" t="inlineStr"/>
+      <c r="B2" s="52" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="53" t="inlineStr">
+        <is>
+          <t>HOW TO USE THIS DASHBOARD</t>
+        </is>
+      </c>
+      <c r="B3" s="52" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="52" t="inlineStr">
+        <is>
+          <t>1.</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="inlineStr">
+        <is>
+          <t>Check the Market Overview tab first — futures and Fed status set the day's tone</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="52" t="inlineStr">
+        <is>
+          <t>2.</t>
+        </is>
+      </c>
+      <c r="B5" s="52" t="inlineStr">
+        <is>
+          <t>Review Top 10 Swing Trades — sorted by Swing Score (volatility + momentum + volume)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="52" t="inlineStr">
+        <is>
+          <t>3.</t>
+        </is>
+      </c>
+      <c r="B6" s="52" t="inlineStr">
+        <is>
+          <t>Check the Buy Signals tab — stocks with BUY rating have the strongest technical setup</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="52" t="inlineStr">
+        <is>
+          <t>4.</t>
+        </is>
+      </c>
+      <c r="B7" s="52" t="inlineStr">
+        <is>
+          <t>NEW: Check Technical Charts tab for visual confirmation of signals</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="52" t="inlineStr">
+        <is>
+          <t>5.</t>
+        </is>
+      </c>
+      <c r="B8" s="52" t="inlineStr">
+        <is>
+          <t>Cross-reference: HIGH Swing Score + BUY rating + chart confirmation = best opportunity</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="52" t="inlineStr">
+        <is>
+          <t>6.</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="inlineStr">
+        <is>
+          <t>Always check if earnings are within 7 days — volatility spikes around reports</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="52" t="inlineStr"/>
+      <c r="B10" s="52" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>RISK MANAGEMENT RULES</t>
+        </is>
+      </c>
+      <c r="B11" s="52" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="52" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="inlineStr">
+        <is>
+          <t>Never risk more than 1-2% of your account on a single swing trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B13" s="52" t="inlineStr">
+        <is>
+          <t>Always set a stop-loss before entering a trade</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="52" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="inlineStr">
+        <is>
+          <t>Take partial profits at 1:1 risk/reward, let remainder run</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="52" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B15" s="52" t="inlineStr">
+        <is>
+          <t>Avoid entering new positions right before major catalysts (earnings, Fed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="52" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B16" s="52" t="inlineStr">
+        <is>
+          <t>Reduce position sizes when VIX is above 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="52" t="inlineStr"/>
+      <c r="B17" s="52" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="53" t="inlineStr">
+        <is>
+          <t>DISCLAIMER</t>
+        </is>
+      </c>
+      <c r="B18" s="52" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="52" t="inlineStr"/>
+      <c r="B19" s="52" t="inlineStr">
+        <is>
+          <t>This spreadsheet is for informational purposes only. Not financial advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="52" t="inlineStr"/>
+      <c r="B20" s="52" t="inlineStr">
+        <is>
+          <t>Swing trading involves significant risk. Past performance doesn't guarantee future results.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>